--- a/ecai_wx/docs/标贝易采_功能点清单.xlsx
+++ b/ecai_wx/docs/标贝易采_功能点清单.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能点清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面结构" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板配置明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面结构" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'功能点清单'!$A$1:$H$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'功能点清单'!$A$1:$H$186</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'功能点清单'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'页面结构'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'模板配置明细'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'页面结构'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -654,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4384,32 +4386,32 @@
       </c>
       <c r="C119" s="27" t="inlineStr">
         <is>
-          <t>任务列表</t>
+          <t>新建/编辑模板</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>任务汇总卡片</t>
+          <t>新建模板初始化</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>展示全部任务、进行中、已暂停和语音任务数量。</t>
+          <t>进入创建模板页面，生成模板草稿并展示模板名称、分类、规范、基础配置和其他配置区域。</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>统计随任务状态变化实时更新。</t>
-        </is>
-      </c>
-      <c r="G119" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>新建时使用默认配置；未保存草稿不得进入正式任务；重复打开不应创建多份空草稿。</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>当前基于页面内 Mock 状态。</t>
+          <t>截图展示为语音采集模板；需接模板创建接口。</t>
         </is>
       </c>
     </row>
@@ -4419,17 +4421,17 @@
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>任务列表展示</t>
+          <t>编辑模板回显</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>展示任务名称、标签、类型、奖励、名额进度、截止日期和状态。</t>
+          <t>编辑已有模板时完整回显模板名称、分类、规范文件及全部模型配置。</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>字段完整；分页正确；状态和名额进度准确。</t>
+          <t>回显值与已发布版本一致；枚举值失效时给出兼容提示；编辑需校验权限。</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -4439,61 +4441,57 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>需支持模板版本与历史配置回溯。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1">
       <c r="A121" s="6" t="n"/>
       <c r="B121" s="6" t="n"/>
-      <c r="C121" s="7" t="n"/>
+      <c r="C121" s="6" t="n"/>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>任务分页</t>
+          <t>模板名称</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>每页展示 10 条任务并支持翻页。</t>
+          <t>填写或修改模板名称，用于任务配置和模板列表识别。</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>总数、页码和每页数量一致。</t>
-        </is>
-      </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>必填；去除首尾空格；长度和重名规则由后台统一校验。</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Ant Design 前端分页已配置。</t>
+          <t>截图默认名称含创建时间，可继续编辑。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1">
       <c r="A122" s="6" t="n"/>
       <c r="B122" s="6" t="n"/>
-      <c r="C122" s="27" t="inlineStr">
-        <is>
-          <t>任务操作</t>
-        </is>
-      </c>
+      <c r="C122" s="6" t="n"/>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>编辑任务</t>
+          <t>模板分类</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>编辑任务配置和内容。</t>
+          <t>选择模板业务类型；当前参考配置为语音采集。</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>权限校验；已产生数据的关键字段限制修改；保存有审计记录。</t>
+          <t>必填；切换分类时动态加载对应配置项；已有数据时需二次确认。</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -4503,71 +4501,67 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>当前仅有编辑图标，无点击逻辑。</t>
+          <t>后续可扩展文本、图片等模板类型。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1">
       <c r="A123" s="6" t="n"/>
       <c r="B123" s="6" t="n"/>
-      <c r="C123" s="7" t="n"/>
+      <c r="C123" s="6" t="n"/>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>暂停/恢复任务</t>
+          <t>模板规范文件</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>进行中任务可暂停，其他任务可按规则恢复或发布。</t>
+          <t>上传模板执行规范，供采集人员或项目成员查看。</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>状态流转合法；暂停后用户端不可新领取。</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>支持 PDF；单文件不超过 10MB；校验文件名、类型、大小、上传失败和替换确认。</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>当前仅有图标，无状态变更逻辑。</t>
+          <t>截图显示拖拽或点击上传 10MB 以内 PDF。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1">
       <c r="A124" s="6" t="n"/>
       <c r="B124" s="6" t="n"/>
-      <c r="C124" s="27" t="inlineStr">
-        <is>
-          <t>新建任务</t>
-        </is>
-      </c>
+      <c r="C124" s="6" t="n"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>任务名称</t>
+          <t>基础配置折叠</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>填写新任务名称。</t>
+          <t>基础配置区域支持展开和收起，减少长表单滚动。</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>必填；长度限制；同项目重名规则。</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>收起不清空已填值；错误配置存在时仍需显示错误提示或定位入口。</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Ant Design 表单仅配置必填。</t>
+          <t>截图右侧提供折叠箭头。</t>
         </is>
       </c>
     </row>
@@ -4577,17 +4571,17 @@
       <c r="C125" s="6" t="n"/>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>采集类型</t>
+          <t>音频格式配置</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>选择语音、文本或图片采集。</t>
+          <t>配置采集端生成的音频文件格式，默认 WAV。</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>单选必填；选择后应展示对应专项配置。</t>
+          <t>必填且单选；保存值必须属于后台枚举；采集端与质检端均能正确录制、播放和解析。</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -4597,7 +4591,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>当前只选择类型，无专项参数。</t>
+          <t>默认 WAV；是否支持 PCM、MP3、FLAC 等其他格式需产品和技术确认。</t>
         </is>
       </c>
     </row>
@@ -4607,17 +4601,17 @@
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>奖励积分</t>
+          <t>声道配置</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>配置单次任务奖励积分。</t>
+          <t>配置录音声道，可选单声道或双声道，建议默认单声道。</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>必填；最小值 1；上限、预算和精度校验。</t>
+          <t>必填且单选；发布前校验目标手机及小程序录音 API 是否支持所选声道；不支持时禁止发布。</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -4627,7 +4621,7 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>当前只校验最小值。</t>
+          <t>需重点验证 Android/iOS 机型对双声道采集的支持情况。</t>
         </is>
       </c>
     </row>
@@ -4637,17 +4631,17 @@
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>总名额</t>
+          <t>采样率配置</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>配置任务可领取总名额。</t>
+          <t>配置音频采样率，可选 16kHz、32kHz、44.1kHz、48kHz，默认 16kHz。</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>必填；整数且大于 0；不可超过项目预算。</t>
+          <t>必填且单选；保存值为 16000/32000/44100/48000；采集端实际文件参数必须与模板一致。</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -4657,7 +4651,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>当前只校验最小值。</t>
+          <t>截图当前只在表格中列了此项；需同时验证不同手机和音频格式的兼容组合。</t>
         </is>
       </c>
     </row>
@@ -4667,17 +4661,17 @@
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>截止日期</t>
+          <t>位深配置</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>配置任务截止日期。</t>
+          <t>配置音频量化位深，可选 16bit 或 32bit，默认 16bit。</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>必填；不得早于当前时间；与项目周期一致。</t>
+          <t>必填且单选；录制文件头及质检解析结果必须与模板配置一致；不支持的设备组合禁止发布。</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -4687,7 +4681,7 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>当前仅使用 date 输入框。</t>
+          <t>截图提供 16/32 两个选项。</t>
         </is>
       </c>
     </row>
@@ -4697,47 +4691,47 @@
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>任务说明</t>
+          <t>噪音上限配置</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>填写用户端展示的任务说明。</t>
+          <t>配置允许的环境噪音阈值，默认值为 70dB，用于采集提示或模型质检。</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>长度和敏感内容校验；支持预览。</t>
-        </is>
-      </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>必填且为非负数；单位固定 dB；允许范围由服务端配置；超过阈值时按规则提示或判定不合格。</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>当前为非必填文本框。</t>
+          <t>需明确该值是声压级、信噪比还是模型评分阈值，避免口径歧义。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1">
       <c r="A130" s="6" t="n"/>
-      <c r="B130" s="7" t="n"/>
-      <c r="C130" s="7" t="n"/>
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>创建任务</t>
+          <t>最大录音时长</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>校验表单后创建任务并加入列表。</t>
+          <t>配置单条录音允许的最大时长，默认 30 秒。</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>接口成功才关闭弹窗；失败保留内容并提示。</t>
+          <t>必填、正数、单位秒；录音达到上限时自动停止并保存；采集端与上传端双重校验。</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -4747,35 +4741,27 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>当前校验后仅关闭弹窗，不会新增记录。</t>
+          <t>截图默认 30 秒；最大允许范围需后台可配置。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1">
       <c r="A131" s="6" t="n"/>
-      <c r="B131" s="28" t="inlineStr">
-        <is>
-          <t>质检管理</t>
-        </is>
-      </c>
-      <c r="C131" s="29" t="inlineStr">
-        <is>
-          <t>质检队列</t>
-        </is>
-      </c>
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>质检状态汇总</t>
+          <t>预留静音段</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>展示待审核、已通过、需返工和已驳回数量。</t>
+          <t>配置录音开始前或提示音后的预留静音时长，默认 1 秒。</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>数量与当前队列一致。</t>
+          <t>取值 0.1-5 秒，步进 0.1 秒；最多保留一位小数；超出范围禁止保存。</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -4785,7 +4771,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>截图说明默认 1 秒。</t>
         </is>
       </c>
     </row>
@@ -4795,17 +4781,17 @@
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>状态筛选</t>
+          <t>录制打点开关</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>按待审核、已通过、需返工、已驳回和全部筛选。</t>
+          <t>控制采集端是否允许在录音过程中添加时间标记。</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>筛选结果与状态数量一致。</t>
+          <t>关闭时隐藏打点入口；开启时采集端必须支持新增、展示和删除打点。</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -4815,7 +4801,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>默认关闭。</t>
         </is>
       </c>
     </row>
@@ -4825,17 +4811,17 @@
       <c r="C133" s="6" t="n"/>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>提交信息</t>
+          <t>多时间戳打点</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>展示任务名称、提交用户和提交时间。</t>
+          <t>录制打点开启后，允许在一条录音中添加多个时间戳，用于问题定位或片段标记。</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>可定位到唯一提交记录。</t>
+          <t>时间戳必须位于 0 到录音时长之间；按时间升序保存；重复时间点去重；停止录音后仍可回显。</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -4845,27 +4831,27 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>需定义每条录音最大打点数量及时间精度。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1">
       <c r="A134" s="6" t="n"/>
       <c r="B134" s="6" t="n"/>
-      <c r="C134" s="7" t="n"/>
+      <c r="C134" s="6" t="n"/>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>AI 评分</t>
+          <t>批注选项管理</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>展示 AI 分数及 AI 通过/拒绝判断。</t>
+          <t>维护采集端或质检端可快速选择的批注标签，支持回车逐项添加。</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>评分范围 0-100；阈值由配置决定。</t>
+          <t>批注项去空格后非空；禁止重复；限制单项长度和总数量；删除已使用项需二次确认。</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -4875,31 +4861,27 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>当前使用 Mock 分数。</t>
+          <t>默认批注项见下方独立配置。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1">
       <c r="A135" s="6" t="n"/>
       <c r="B135" s="6" t="n"/>
-      <c r="C135" s="29" t="inlineStr">
-        <is>
-          <t>质检详情</t>
-        </is>
-      </c>
+      <c r="C135" s="6" t="n"/>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>语音数据预览</t>
+          <t>批注项：有环境噪音</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>展示语音时长、格式和波形，并应支持播放。</t>
+          <t>标记录音中存在街道、人群、风声或其他环境背景噪音。</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>文件可访问；格式、采样率和时长正确；支持异常文件提示。</t>
+          <t>默认启用；可多选；提交后保存到当前录音的质检标签。</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -4909,7 +4891,7 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>当前仅模拟波形，不可播放。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -4919,17 +4901,17 @@
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>文本内容预览</t>
+          <t>批注项：有电流/电子噪音</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>完整展示待审核文本内容。</t>
+          <t>标记录音中存在电流声、底噪、蜂鸣或设备电子干扰。</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>保留换行；超长内容可滚动；敏感信息按规则处理。</t>
+          <t>默认启用；可多选；标签编码需稳定，避免仅保存显示文案。</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -4939,7 +4921,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4931,17 @@
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>图片数据预览</t>
+          <t>批注项：有回音/空旷音</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>以网格展示提交图片。</t>
+          <t>标记录音环境混响明显、空间空旷或回声影响清晰度。</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>支持大图查看、切换和加载失败提示。</t>
+          <t>默认启用；可多选；与环境噪音标签允许同时选择。</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -4969,7 +4951,7 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>当前只有彩色占位块，不是真实图片。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -4979,17 +4961,17 @@
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>审核通过</t>
+          <t>批注项：中间停顿时间过长</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>人工确认数据合格，进入积分结算。</t>
+          <t>标记录音内容中出现不符合要求的长时间停顿。</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>二次确认或权限校验；写入审核人、时间和意见。</t>
+          <t>默认启用；可多选；停顿判定阈值应由验收规则或模型配置明确。</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -4999,7 +4981,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>当前仅更新页面内状态。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -5009,17 +4991,17 @@
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>要求返工</t>
+          <t>批注项：录音与文本不一致</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>将提交退回用户并要求修改。</t>
+          <t>标记朗读内容存在漏读、错读、增读或顺序与目标文本不一致。</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>必须填写返工原因；用户端可收到并定位问题。</t>
+          <t>默认启用；可多选；应支持关联问题文本或时间点。</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -5029,27 +5011,27 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>当前无需填写原因，直接更新状态。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1">
       <c r="A140" s="6" t="n"/>
-      <c r="B140" s="7" t="n"/>
-      <c r="C140" s="7" t="n"/>
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>驳回提交</t>
+          <t>批注项：有喷麦/录音距离太近</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>判定提交无效并关闭该次提交。</t>
+          <t>标记爆破音明显或录音设备距离过近导致失真。</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>必须填写驳回原因；涉及扣回时需走积分账本。</t>
+          <t>默认启用；可多选；可与音量过大类问题同时出现。</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -5059,69 +5041,57 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>当前无需原因，直接更新状态。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1">
       <c r="A141" s="6" t="n"/>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>用户管理</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>用户概览</t>
-        </is>
-      </c>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>用户统计</t>
+          <t>批注项：没有人声</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>展示总用户、已实名、有标签和 Lv4+ 高等级用户数量。</t>
+          <t>标记录音文件为空、只有背景声或未检测到有效人声。</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>统计与用户筛选口径一致。</t>
-        </is>
-      </c>
-      <c r="G141" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>默认启用；命中时应禁止直接判定为合格；模型检测与人工质检结果需一致。</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>当前使用 Mock 用户。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1">
       <c r="A142" s="6" t="n"/>
       <c r="B142" s="6" t="n"/>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>用户列表</t>
-        </is>
-      </c>
+      <c r="C142" s="6" t="n"/>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>用户搜索</t>
+          <t>批注项：只需朗读一遍文本</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>按昵称或手机号搜索用户。</t>
+          <t>标记录音中目标文本被重复朗读，需要提示仅朗读一次。</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>支持模糊匹配；手机号查询权限受控。</t>
+          <t>默认启用；可多选；命中文案需同步给返工用户。</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -5131,7 +5101,7 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>原型已实现前端过滤。</t>
+          <t>根据截图原文保留该批注名称。</t>
         </is>
       </c>
     </row>
@@ -5141,27 +5111,27 @@
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>标签筛选</t>
+          <t>批注项：前后静音段预留不足</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>从现有标签中筛选用户。</t>
+          <t>标记录音开头或结尾缺少模板要求的静音缓冲。</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>支持清空筛选；标签字典一致。</t>
-        </is>
-      </c>
-      <c r="G143" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>默认启用；可多选；静音段要求应与“预留静音段”配置联动。</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>原型已实现单标签过滤。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -5171,17 +5141,17 @@
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>用户信息展示</t>
+          <t>批注项：语速过慢不符合描述</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>展示头像、昵称、手机号、语言、标签、等级和积分。</t>
+          <t>标记录音语速低于任务说明或模板验收要求。</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>敏感手机号脱敏；数据字段完整。</t>
+          <t>默认启用；可多选；语速范围或模型阈值需有统一口径。</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -5191,7 +5161,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>当前展示 Mock 手机号。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
@@ -5201,81 +5171,77 @@
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>任务与通过率</t>
+          <t>批注项：语速过快听不清楚</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>展示用户任务数量和通过率进度。</t>
+          <t>标记录音语速过快，影响内容辨识。</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>通过率口径明确，分母为已审核任务。</t>
-        </is>
-      </c>
-      <c r="G145" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>默认启用；可多选；返工提示需明确要求降低语速。</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>当前使用 Mock 字段。</t>
+          <t>截图默认批注项。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1">
       <c r="A146" s="6" t="n"/>
       <c r="B146" s="6" t="n"/>
-      <c r="C146" s="7" t="n"/>
+      <c r="C146" s="6" t="n"/>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>实名与账号状态</t>
+          <t>批注项：语速区分不清晰</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>展示已实名/未实名以及正常/封禁状态。</t>
+          <t>标记录音中的语速、节奏或停连不清晰，无法满足任务描述。</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>状态与权限控制一致。</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>默认启用；可多选；该标签与“语速过快/过慢”的边界需在质检规范中定义。</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>原型已实现展示。</t>
+          <t>根据截图原文保留；建议产品评审时确认最终命名。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="42" customHeight="1">
       <c r="A147" s="6" t="n"/>
-      <c r="B147" s="7" t="n"/>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>用户详情</t>
-        </is>
-      </c>
+      <c r="B147" s="6" t="n"/>
+      <c r="C147" s="6" t="n"/>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>查看用户详情</t>
+          <t>DIY 自定义说明</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>进入用户详情查看档案、任务、积分和审核记录。</t>
+          <t>提供多行文本框，用于填写默认批注无法覆盖的模板补充要求。</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>权限控制；敏感字段审计。</t>
+          <t>可选；限制最大长度；保留换行；过滤危险脚本；保存后在预览和采集/质检端按规则展示。</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -5285,69 +5251,57 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>当前详情按钮无点击逻辑。</t>
+          <t>截图显示 DIY 输入框。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="42" customHeight="1">
       <c r="A148" s="6" t="n"/>
-      <c r="B148" s="21" t="inlineStr">
-        <is>
-          <t>结算中心</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="inlineStr">
-        <is>
-          <t>结算概览</t>
-        </is>
-      </c>
+      <c r="B148" s="6" t="n"/>
+      <c r="C148" s="6" t="n"/>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>结算统计</t>
+          <t>模板预览</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>展示待审核提现、处理中、已到账金额和累计手续费。</t>
+          <t>在保存或发布前预览采集端实际看到的配置、提示和批注项。</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>与提现流水实时一致。</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>预览数据必须取当前未保存表单值；不同设备视图与最终采集端一致。</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>当前使用 Mock 数据。</t>
+          <t>截图顶部提供“预览”按钮。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="42" customHeight="1">
       <c r="A149" s="6" t="n"/>
       <c r="B149" s="6" t="n"/>
-      <c r="C149" s="22" t="inlineStr">
-        <is>
-          <t>提现审核</t>
-        </is>
-      </c>
+      <c r="C149" s="6" t="n"/>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>提现申请列表</t>
+          <t>保存模板</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>展示申请用户、申请时间、金额、手续费、实际到账和状态。</t>
+          <t>校验全部配置后保存模板草稿或新版本。</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>金额精度、费率和状态准确；支持分页。</t>
+          <t>存在必填、范围、兼容性错误时禁止保存并定位字段；保存成功返回明确反馈；防重复提交。</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -5357,7 +5311,7 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>原型已实现。</t>
+          <t>编辑已使用模板时建议生成新版本，避免影响进行中任务。</t>
         </is>
       </c>
     </row>
@@ -5367,126 +5321,1168 @@
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>审核通过确认</t>
+          <t>关闭页面</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>弹窗复核用户、申请金额、手续费和实际到账后确认打款。</t>
+          <t>关闭模板编辑页面并返回模板列表或上一页。</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>仅待审核可操作；权限校验；确认后不可重复处理。</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>存在未保存修改时必须二次确认；选择取消后保留当前内容。</t>
+        </is>
+      </c>
+      <c r="G150" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>当前仅更新为处理中，不调用支付。</t>
+          <t>截图顶部提供“关闭”按钮。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="42" customHeight="1">
       <c r="A151" s="6" t="n"/>
       <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
+      <c r="C151" s="7" t="n"/>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>审核拒绝</t>
+          <t>更多操作</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>拒绝提现申请并记录失败状态。</t>
+          <t>承载复制模板、另存为、停用、删除或查看版本等扩展操作。</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>必须填写原因；解冻或退回积分；通知用户。</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>按模板状态和管理员权限展示；删除、停用等高风险动作需二次确认和审计。</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>当前直接更新为失败，无原因和积分回滚。</t>
+          <t>截图只有“更多”入口，具体菜单需产品确认。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="42" customHeight="1">
       <c r="A152" s="6" t="n"/>
       <c r="B152" s="6" t="n"/>
-      <c r="C152" s="7" t="n"/>
+      <c r="C152" s="27" t="inlineStr">
+        <is>
+          <t>任务列表</t>
+        </is>
+      </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
+          <t>任务汇总卡片</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>展示全部任务、进行中、已暂停和语音任务数量。</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>统计随任务状态变化实时更新。</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>当前基于页面内 Mock 状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="6" t="n"/>
+      <c r="B153" s="6" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>任务列表展示</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>展示任务名称、标签、类型、奖励、名额进度、截止日期和状态。</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>字段完整；分页正确；状态和名额进度准确。</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="6" t="n"/>
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>任务分页</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>每页展示 10 条任务并支持翻页。</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>总数、页码和每页数量一致。</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>Ant Design 前端分页已配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="6" t="n"/>
+      <c r="B155" s="6" t="n"/>
+      <c r="C155" s="27" t="inlineStr">
+        <is>
+          <t>任务操作</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>编辑任务</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>编辑任务配置和内容。</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>权限校验；已产生数据的关键字段限制修改；保存有审计记录。</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>当前仅有编辑图标，无点击逻辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="6" t="n"/>
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>暂停/恢复任务</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>进行中任务可暂停，其他任务可按规则恢复或发布。</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>状态流转合法；暂停后用户端不可新领取。</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>当前仅有图标，无状态变更逻辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="6" t="n"/>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="27" t="inlineStr">
+        <is>
+          <t>新建任务</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>任务名称</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>填写新任务名称。</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>必填；长度限制；同项目重名规则。</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Ant Design 表单仅配置必填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="6" t="n"/>
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>采集类型</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>选择语音、文本或图片采集。</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>单选必填；选择后应展示对应专项配置。</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>当前只选择类型，无专项参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="6" t="n"/>
+      <c r="B159" s="6" t="n"/>
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>奖励积分</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>配置单次任务奖励积分。</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>必填；最小值 1；上限、预算和精度校验。</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>当前只校验最小值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="6" t="n"/>
+      <c r="B160" s="6" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>总名额</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>配置任务可领取总名额。</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>必填；整数且大于 0；不可超过项目预算。</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>当前只校验最小值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="6" t="n"/>
+      <c r="B161" s="6" t="n"/>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>截止日期</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>配置任务截止日期。</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>必填；不得早于当前时间；与项目周期一致。</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>当前仅使用 date 输入框。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="6" t="n"/>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>任务说明</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>填写用户端展示的任务说明。</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>长度和敏感内容校验；支持预览。</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>当前为非必填文本框。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="6" t="n"/>
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="7" t="n"/>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>创建任务</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>校验表单后创建任务并加入列表。</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>接口成功才关闭弹窗；失败保留内容并提示。</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>当前校验后仅关闭弹窗，不会新增记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="6" t="n"/>
+      <c r="B164" s="28" t="inlineStr">
+        <is>
+          <t>质检管理</t>
+        </is>
+      </c>
+      <c r="C164" s="29" t="inlineStr">
+        <is>
+          <t>质检队列</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>质检状态汇总</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>展示待审核、已通过、需返工和已驳回数量。</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>数量与当前队列一致。</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="6" t="n"/>
+      <c r="B165" s="6" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>状态筛选</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>按待审核、已通过、需返工、已驳回和全部筛选。</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>筛选结果与状态数量一致。</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="6" t="n"/>
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>提交信息</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>展示任务名称、提交用户和提交时间。</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>可定位到唯一提交记录。</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="6" t="n"/>
+      <c r="B167" s="6" t="n"/>
+      <c r="C167" s="7" t="n"/>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>AI 评分</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>展示 AI 分数及 AI 通过/拒绝判断。</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>评分范围 0-100；阈值由配置决定。</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>当前使用 Mock 分数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="6" t="n"/>
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="29" t="inlineStr">
+        <is>
+          <t>质检详情</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>语音数据预览</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>展示语音时长、格式和波形，并应支持播放。</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>文件可访问；格式、采样率和时长正确；支持异常文件提示。</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>当前仅模拟波形，不可播放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="6" t="n"/>
+      <c r="B169" s="6" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>文本内容预览</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>完整展示待审核文本内容。</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>保留换行；超长内容可滚动；敏感信息按规则处理。</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="6" t="n"/>
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>图片数据预览</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>以网格展示提交图片。</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>支持大图查看、切换和加载失败提示。</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>当前只有彩色占位块，不是真实图片。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="6" t="n"/>
+      <c r="B171" s="6" t="n"/>
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>审核通过</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>人工确认数据合格，进入积分结算。</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>二次确认或权限校验；写入审核人、时间和意见。</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>当前仅更新页面内状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="6" t="n"/>
+      <c r="B172" s="6" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>要求返工</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>将提交退回用户并要求修改。</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>必须填写返工原因；用户端可收到并定位问题。</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>当前无需填写原因，直接更新状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="6" t="n"/>
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="7" t="n"/>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>驳回提交</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>判定提交无效并关闭该次提交。</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>必须填写驳回原因；涉及扣回时需走积分账本。</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>当前无需原因，直接更新状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="6" t="n"/>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>用户概览</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>用户统计</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>展示总用户、已实名、有标签和 Lv4+ 高等级用户数量。</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>统计与用户筛选口径一致。</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>当前使用 Mock 用户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="6" t="n"/>
+      <c r="B175" s="6" t="n"/>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>用户列表</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>用户搜索</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>按昵称或手机号搜索用户。</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>支持模糊匹配；手机号查询权限受控。</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现前端过滤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="6" t="n"/>
+      <c r="B176" s="6" t="n"/>
+      <c r="C176" s="6" t="n"/>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>标签筛选</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>从现有标签中筛选用户。</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>支持清空筛选；标签字典一致。</t>
+        </is>
+      </c>
+      <c r="G176" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现单标签过滤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="6" t="n"/>
+      <c r="B177" s="6" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>用户信息展示</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>展示头像、昵称、手机号、语言、标签、等级和积分。</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>敏感手机号脱敏；数据字段完整。</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>当前展示 Mock 手机号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="6" t="n"/>
+      <c r="B178" s="6" t="n"/>
+      <c r="C178" s="6" t="n"/>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>任务与通过率</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>展示用户任务数量和通过率进度。</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>通过率口径明确，分母为已审核任务。</t>
+        </is>
+      </c>
+      <c r="G178" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>当前使用 Mock 字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="42" customHeight="1">
+      <c r="A179" s="6" t="n"/>
+      <c r="B179" s="6" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>实名与账号状态</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>展示已实名/未实名以及正常/封禁状态。</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>状态与权限控制一致。</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现展示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="42" customHeight="1">
+      <c r="A180" s="6" t="n"/>
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>用户详情</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>查看用户详情</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>进入用户详情查看档案、任务、积分和审核记录。</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>权限控制；敏感字段审计。</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>当前详情按钮无点击逻辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="6" t="n"/>
+      <c r="B181" s="21" t="inlineStr">
+        <is>
+          <t>结算中心</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="inlineStr">
+        <is>
+          <t>结算概览</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>结算统计</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>展示待审核提现、处理中、已到账金额和累计手续费。</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>与提现流水实时一致。</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>当前使用 Mock 数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="6" t="n"/>
+      <c r="B182" s="6" t="n"/>
+      <c r="C182" s="22" t="inlineStr">
+        <is>
+          <t>提现审核</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>提现申请列表</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>展示申请用户、申请时间、金额、手续费、实际到账和状态。</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>金额精度、费率和状态准确；支持分页。</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>原型已实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="42" customHeight="1">
+      <c r="A183" s="6" t="n"/>
+      <c r="B183" s="6" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>审核通过确认</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>弹窗复核用户、申请金额、手续费和实际到账后确认打款。</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>仅待审核可操作；权限校验；确认后不可重复处理。</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>当前仅更新为处理中，不调用支付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="42" customHeight="1">
+      <c r="A184" s="6" t="n"/>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>审核拒绝</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>拒绝提现申请并记录失败状态。</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>必须填写原因；解冻或退回积分；通知用户。</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>当前直接更新为失败，无原因和积分回滚。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="42" customHeight="1">
+      <c r="A185" s="6" t="n"/>
+      <c r="B185" s="6" t="n"/>
+      <c r="C185" s="7" t="n"/>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
           <t>提现详情</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
+      <c r="E185" s="4" t="inlineStr">
         <is>
           <t>查看申请、实名核验、支付单号和状态流转记录。</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>信息完整且可审计。</t>
         </is>
       </c>
-      <c r="G152" s="10" t="inlineStr">
+      <c r="G185" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
+      <c r="H185" s="4" t="inlineStr">
         <is>
           <t>当前详情按钮无点击逻辑。</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="42" customHeight="1">
-      <c r="A153" s="7" t="n"/>
-      <c r="B153" s="7" t="n"/>
-      <c r="C153" s="22" t="inlineStr">
+    <row r="186" ht="42" customHeight="1">
+      <c r="A186" s="7" t="n"/>
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="22" t="inlineStr">
         <is>
           <t>积分流水</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>积分流水列表</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="E186" s="4" t="inlineStr">
         <is>
           <t>展示描述、类型、增减积分和发生时间。</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>与用户端流水一致；支持按用户、类型和时间查询。</t>
         </is>
       </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
         <is>
           <t>当前只展示 Mock 列表，无筛选。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H153">
+  <autoFilter ref="A1:H186">
     <filterColumn colId="6" hiddenButton="0" showButton="1">
       <filters blank="0">
         <filter val="P0"/>
@@ -5495,11 +6491,10 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="44">
+  <mergeCells count="45">
     <mergeCell ref="C37:C44"/>
     <mergeCell ref="C103:C104"/>
     <mergeCell ref="B97:B102"/>
-    <mergeCell ref="C119:C121"/>
     <mergeCell ref="B4:B11"/>
     <mergeCell ref="C52:C58"/>
     <mergeCell ref="C12:C20"/>
@@ -5508,38 +6503,40 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B112:B118"/>
     <mergeCell ref="C97:C102"/>
+    <mergeCell ref="C168:C173"/>
     <mergeCell ref="C64:C71"/>
+    <mergeCell ref="B174:B180"/>
     <mergeCell ref="C112:C115"/>
-    <mergeCell ref="B148:B153"/>
     <mergeCell ref="C72:C78"/>
     <mergeCell ref="B37:B58"/>
+    <mergeCell ref="C164:C167"/>
     <mergeCell ref="B103:B106"/>
     <mergeCell ref="B59:B63"/>
-    <mergeCell ref="B131:B140"/>
+    <mergeCell ref="B181:B186"/>
     <mergeCell ref="B84:B96"/>
     <mergeCell ref="C116:C118"/>
+    <mergeCell ref="C119:C151"/>
     <mergeCell ref="B64:B83"/>
     <mergeCell ref="C95:C96"/>
-    <mergeCell ref="B141:B147"/>
+    <mergeCell ref="C182:C185"/>
     <mergeCell ref="B12:B36"/>
-    <mergeCell ref="A107:A153"/>
-    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="A107:A186"/>
     <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C175:C179"/>
     <mergeCell ref="C107:C111"/>
     <mergeCell ref="A2:A106"/>
     <mergeCell ref="C89:C93"/>
+    <mergeCell ref="C157:C163"/>
     <mergeCell ref="C79:C83"/>
     <mergeCell ref="C30:C36"/>
     <mergeCell ref="C45:C51"/>
-    <mergeCell ref="C131:C134"/>
-    <mergeCell ref="C135:C140"/>
-    <mergeCell ref="B119:B130"/>
-    <mergeCell ref="C142:C146"/>
-    <mergeCell ref="C149:C152"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="B119:B163"/>
+    <mergeCell ref="C152:C154"/>
     <mergeCell ref="B107:B111"/>
     <mergeCell ref="C84:C88"/>
     <mergeCell ref="C59:C63"/>
-    <mergeCell ref="C124:C130"/>
+    <mergeCell ref="B164:B173"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -5547,6 +6544,1080 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>客户端</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>二级模块</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>功能点</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>解释</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>校验</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>新建/编辑模板</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>新建模板初始化</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>进入创建模板页面，生成模板草稿并展示模板名称、分类、规范、基础配置和其他配置区域。</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>新建时使用默认配置；未保存草稿不得进入正式任务；重复打开不应创建多份空草稿。</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>截图展示为语音采集模板；需接模板创建接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>编辑模板回显</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>编辑已有模板时完整回显模板名称、分类、规范文件及全部模型配置。</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>回显值与已发布版本一致；枚举值失效时给出兼容提示；编辑需校验权限。</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>需支持模板版本与历史配置回溯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>模板名称</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>填写或修改模板名称，用于任务配置和模板列表识别。</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>必填；去除首尾空格；长度和重名规则由后台统一校验。</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>截图默认名称含创建时间，可继续编辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>模板分类</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>选择模板业务类型；当前参考配置为语音采集。</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>必填；切换分类时动态加载对应配置项；已有数据时需二次确认。</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>后续可扩展文本、图片等模板类型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>模板规范文件</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>上传模板执行规范，供采集人员或项目成员查看。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>支持 PDF；单文件不超过 10MB；校验文件名、类型、大小、上传失败和替换确认。</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>截图显示拖拽或点击上传 10MB 以内 PDF。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>基础配置折叠</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>基础配置区域支持展开和收起，减少长表单滚动。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>收起不清空已填值；错误配置存在时仍需显示错误提示或定位入口。</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>截图右侧提供折叠箭头。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>音频格式配置</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>配置采集端生成的音频文件格式，默认 WAV。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>必填且单选；保存值必须属于后台枚举；采集端与质检端均能正确录制、播放和解析。</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>默认 WAV；是否支持 PCM、MP3、FLAC 等其他格式需产品和技术确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>声道配置</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>配置录音声道，可选单声道或双声道，建议默认单声道。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>必填且单选；发布前校验目标手机及小程序录音 API 是否支持所选声道；不支持时禁止发布。</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>需重点验证 Android/iOS 机型对双声道采集的支持情况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>采样率配置</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>配置音频采样率，可选 16kHz、32kHz、44.1kHz、48kHz，默认 16kHz。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>必填且单选；保存值为 16000/32000/44100/48000；采集端实际文件参数必须与模板一致。</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>截图当前只在表格中列了此项；需同时验证不同手机和音频格式的兼容组合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>位深配置</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>配置音频量化位深，可选 16bit 或 32bit，默认 16bit。</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>必填且单选；录制文件头及质检解析结果必须与模板配置一致；不支持的设备组合禁止发布。</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>截图提供 16/32 两个选项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>噪音上限配置</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>配置允许的环境噪音阈值，默认值为 70dB，用于采集提示或模型质检。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>必填且为非负数；单位固定 dB；允许范围由服务端配置；超过阈值时按规则提示或判定不合格。</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>需明确该值是声压级、信噪比还是模型评分阈值，避免口径歧义。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>最大录音时长</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>配置单条录音允许的最大时长，默认 30 秒。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>必填、正数、单位秒；录音达到上限时自动停止并保存；采集端与上传端双重校验。</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>截图默认 30 秒；最大允许范围需后台可配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>预留静音段</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>配置录音开始前或提示音后的预留静音时长，默认 1 秒。</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>取值 0.1-5 秒，步进 0.1 秒；最多保留一位小数；超出范围禁止保存。</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>截图说明默认 1 秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>录制打点开关</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>控制采集端是否允许在录音过程中添加时间标记。</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>关闭时隐藏打点入口；开启时采集端必须支持新增、展示和删除打点。</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>默认关闭。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>多时间戳打点</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>录制打点开启后，允许在一条录音中添加多个时间戳，用于问题定位或片段标记。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>时间戳必须位于 0 到录音时长之间；按时间升序保存；重复时间点去重；停止录音后仍可回显。</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>需定义每条录音最大打点数量及时间精度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>批注选项管理</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>维护采集端或质检端可快速选择的批注标签，支持回车逐项添加。</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>批注项去空格后非空；禁止重复；限制单项长度和总数量；删除已使用项需二次确认。</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>默认批注项见下方独立配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>批注项：有环境噪音</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>标记录音中存在街道、人群、风声或其他环境背景噪音。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；提交后保存到当前录音的质检标签。</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>批注项：有电流/电子噪音</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>标记录音中存在电流声、底噪、蜂鸣或设备电子干扰。</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；标签编码需稳定，避免仅保存显示文案。</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>批注项：有回音/空旷音</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>标记录音环境混响明显、空间空旷或回声影响清晰度。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；与环境噪音标签允许同时选择。</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>批注项：中间停顿时间过长</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>标记录音内容中出现不符合要求的长时间停顿。</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；停顿判定阈值应由验收规则或模型配置明确。</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>批注项：录音与文本不一致</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>标记朗读内容存在漏读、错读、增读或顺序与目标文本不一致。</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；应支持关联问题文本或时间点。</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>批注项：有喷麦/录音距离太近</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>标记爆破音明显或录音设备距离过近导致失真。</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；可与音量过大类问题同时出现。</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>批注项：没有人声</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>标记录音文件为空、只有背景声或未检测到有效人声。</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；命中时应禁止直接判定为合格；模型检测与人工质检结果需一致。</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>批注项：只需朗读一遍文本</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>标记录音中目标文本被重复朗读，需要提示仅朗读一次。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；命中文案需同步给返工用户。</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>根据截图原文保留该批注名称。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>批注项：前后静音段预留不足</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>标记录音开头或结尾缺少模板要求的静音缓冲。</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；静音段要求应与“预留静音段”配置联动。</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>批注项：语速过慢不符合描述</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>标记录音语速低于任务说明或模板验收要求。</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；语速范围或模型阈值需有统一口径。</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>批注项：语速过快听不清楚</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>标记录音语速过快，影响内容辨识。</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；返工提示需明确要求降低语速。</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>截图默认批注项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>批注项：语速区分不清晰</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>标记录音中的语速、节奏或停连不清晰，无法满足任务描述。</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>默认启用；可多选；该标签与“语速过快/过慢”的边界需在质检规范中定义。</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>根据截图原文保留；建议产品评审时确认最终命名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>DIY 自定义说明</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>提供多行文本框，用于填写默认批注无法覆盖的模板补充要求。</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>可选；限制最大长度；保留换行；过滤危险脚本；保存后在预览和采集/质检端按规则展示。</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>截图显示 DIY 输入框。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>模板预览</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>在保存或发布前预览采集端实际看到的配置、提示和批注项。</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>预览数据必须取当前未保存表单值；不同设备视图与最终采集端一致。</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>截图顶部提供“预览”按钮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>保存模板</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>校验全部配置后保存模板草稿或新版本。</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>存在必填、范围、兼容性错误时禁止保存并定位字段；保存成功返回明确反馈；防重复提交。</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>编辑已使用模板时建议生成新版本，避免影响进行中任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>关闭页面</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>关闭模板编辑页面并返回模板列表或上一页。</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>存在未保存修改时必须二次确认；选择取消后保留当前内容。</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>截图顶部提供“关闭”按钮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>更多操作</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>承载复制模板、另存为、停用、删除或查看版本等扩展操作。</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>按模板状态和管理员权限展示；删除、停用等高风险动作需二次确认和审计。</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>截图只有“更多”入口，具体菜单需产品确认。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H34"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A34"/>
+    <mergeCell ref="C2:C34"/>
+    <mergeCell ref="B2:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6135,7 +8206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6179,7 +8250,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>152</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
